--- a/Data/Building/MeetingRoomOne.HumanState.xlsx
+++ b/Data/Building/MeetingRoomOne.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709255950</v>
+        <v>1711847160</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709258874</v>
+        <v>1711852621</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260182</v>
+        <v>1711857747</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262949</v>
+        <v>1711859039</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709267048</v>
+        <v>1711859677</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +642,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709270761</v>
+        <v>1711861908</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +698,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709249516</v>
+        <v>1711927996</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +712,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +731,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709252089</v>
+        <v>1711930396</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +745,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +768,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709253090</v>
+        <v>1711930628</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +782,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +801,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709254559</v>
+        <v>1711932481</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +815,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +838,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709258309</v>
+        <v>1711933160</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +852,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +871,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709262800</v>
+        <v>1711934841</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +885,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +908,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709336398</v>
+        <v>1711936114</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +922,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +941,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709339131</v>
+        <v>1711938803</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +955,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +978,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709339148</v>
+        <v>1712014741</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +992,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1011,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709340377</v>
+        <v>1712018440</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1025,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1044,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709344278</v>
+        <v>1712018815</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1058,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1077,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709346381</v>
+        <v>1712021072</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1091,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1110,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709346857</v>
+        <v>1712024565</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1124,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1143,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709348861</v>
+        <v>1712028463</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1157,11 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1180,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709422378</v>
+        <v>1712102397</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1194,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1213,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709425362</v>
+        <v>1712104283</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1227,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1250,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709425435</v>
+        <v>1712106537</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1264,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1283,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709429557</v>
+        <v>1712109801</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1297,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1320,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709430710</v>
+        <v>1712110980</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1334,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1353,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709431681</v>
+        <v>1712115747</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1367,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1390,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709431780</v>
+        <v>1712186105</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1404,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1423,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709436376</v>
+        <v>1712190390</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1437,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1460,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709508362</v>
+        <v>1712191414</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1474,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1493,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709513236</v>
+        <v>1712195482</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1507,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1530,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709516998</v>
+        <v>1712195629</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1544,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709521778</v>
+        <v>1712198553</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1577,11 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1600,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709596577</v>
+        <v>1712198583</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1614,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1633,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709602255</v>
+        <v>1712200248</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1647,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1670,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709606974</v>
+        <v>1712272830</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1684,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1703,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709609257</v>
+        <v>1712274799</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1717,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1736,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709852790</v>
+        <v>1712275384</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1750,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1769,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709856550</v>
+        <v>1712277825</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1783,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1806,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709860867</v>
+        <v>1712282557</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1820,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1839,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709865294</v>
+        <v>1712287829</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1853,11 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1876,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709939631</v>
+        <v>1712533697</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1890,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1909,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709942536</v>
+        <v>1712536898</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1923,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1942,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709942679</v>
+        <v>1712536994</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1956,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1975,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709946513</v>
+        <v>1712540397</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1989,11 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2012,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709950287</v>
+        <v>1712542402</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2026,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2045,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709952473</v>
+        <v>1712547597</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2059,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2082,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710027999</v>
+        <v>1712621506</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2096,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2115,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710029647</v>
+        <v>1712624527</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2129,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2152,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710029749</v>
+        <v>1712625103</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2166,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2185,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710035299</v>
+        <v>1712629662</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2199,11 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2222,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710036054</v>
+        <v>1712630424</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2236,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2255,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710037309</v>
+        <v>1712632691</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2269,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2292,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710038905</v>
+        <v>1712707862</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2306,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2325,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710042721</v>
+        <v>1712711847</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2339,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2362,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710115282</v>
+        <v>1712711974</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2376,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2395,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710117969</v>
+        <v>1712713009</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2409,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2432,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710118794</v>
+        <v>1712716895</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2446,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2465,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710120459</v>
+        <v>1712720335</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2479,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2502,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710125679</v>
+        <v>1712794829</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2516,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2535,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710130140</v>
+        <v>1712799824</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2549,11 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2572,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710200213</v>
+        <v>1712804006</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2586,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2605,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710203318</v>
+        <v>1712807131</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2619,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2642,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710204410</v>
+        <v>1712879334</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2656,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2675,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710205419</v>
+        <v>1712882536</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2689,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2708,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710205722</v>
+        <v>1712883537</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2722,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2741,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710207217</v>
+        <v>1712885436</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2755,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2778,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710207407</v>
+        <v>1712887150</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2792,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2811,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710209747</v>
+        <v>1712891708</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2825,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2848,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710210385</v>
+        <v>1713137399</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2862,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2881,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710214759</v>
+        <v>1713138890</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2895,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2918,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710459580</v>
+        <v>1713139096</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2932,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2951,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710462700</v>
+        <v>1713141611</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2965,11 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2988,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710463304</v>
+        <v>1713145756</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +3002,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +3021,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710464684</v>
+        <v>1713150890</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3035,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3058,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710464914</v>
+        <v>1713223462</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3072,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3091,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710467474</v>
+        <v>1713225292</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3105,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3124,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710469214</v>
+        <v>1713225535</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3138,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3157,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710472668</v>
+        <v>1713227676</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3171,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3194,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710545475</v>
+        <v>1713230250</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3208,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3227,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710549753</v>
+        <v>1713234442</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3241,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3264,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710553370</v>
+        <v>1713310747</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3278,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3297,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710555284</v>
+        <v>1713315390</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3311,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3334,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710555461</v>
+        <v>1713318856</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3348,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3367,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710559633</v>
+        <v>1713322119</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3381,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3404,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710634158</v>
+        <v>1713395533</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3418,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3437,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710637014</v>
+        <v>1713399659</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3451,11 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3474,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710637171</v>
+        <v>1713403659</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3488,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3507,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710641640</v>
+        <v>1713406318</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3521,11 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3544,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710642720</v>
+        <v>1713484650</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3558,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3577,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710645882</v>
+        <v>1713486130</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3591,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3610,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710719490</v>
+        <v>1713486159</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3624,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3643,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710723871</v>
+        <v>1713488144</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3657,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3676,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710727830</v>
+        <v>1713488154</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3690,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3709,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710728833</v>
+        <v>1713489110</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3723,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3746,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710728872</v>
+        <v>1713491005</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3760,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3779,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710731892</v>
+        <v>1713495260</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3793,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3816,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710805948</v>
+        <v>1713741360</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3830,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3849,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710808015</v>
+        <v>1713743230</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3863,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3882,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710808799</v>
+        <v>1713744163</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3896,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3915,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710811873</v>
+        <v>1713748917</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3929,11 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3952,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710815399</v>
+        <v>1713750195</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3966,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3985,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710818352</v>
+        <v>1713753030</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3999,11 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +4022,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711064080</v>
+        <v>1713828830</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +4036,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +4055,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711068734</v>
+        <v>1713832979</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4069,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4092,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711072645</v>
+        <v>1713833141</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4106,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4125,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711075317</v>
+        <v>1713835289</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4139,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4162,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711150328</v>
+        <v>1713837275</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4176,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4195,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711152632</v>
+        <v>1713839986</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4209,11 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4232,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711153412</v>
+        <v>1713840438</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4246,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4265,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711154840</v>
+        <v>1713844335</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4279,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4298,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711160434</v>
+        <v>1713915093</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4312,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4331,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711164236</v>
+        <v>1713920061</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4345,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4364,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711236324</v>
+        <v>1713922860</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4378,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4397,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711238266</v>
+        <v>1713924720</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4411,11 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4434,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711239826</v>
+        <v>1713925890</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4448,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4467,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711242824</v>
+        <v>1713928714</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4481,11 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4504,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711243026</v>
+        <v>1714000052</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4518,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4537,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711244462</v>
+        <v>1714004156</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4551,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4570,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711246126</v>
+        <v>1714004245</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4584,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4603,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711250791</v>
+        <v>1714006890</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4617,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4640,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711323216</v>
+        <v>1714007316</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4654,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4673,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711326474</v>
+        <v>1714010875</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4687,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4710,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711326592</v>
+        <v>1714086812</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4724,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4743,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711328848</v>
+        <v>1714090690</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4757,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4780,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711331407</v>
+        <v>1714094076</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4794,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4813,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711335986</v>
+        <v>1714098506</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,262 +4827,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1711410243</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Detected</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1711413230</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Undetected</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1711413566</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Detected</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1711415838</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Undetected</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>1711416863</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Detected</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1711418687</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Undetected</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>1711420480</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Detected</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>HumanDetected_Change</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1711423926</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.HumanState.state: Undetected</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
